--- a/research/traditional_assets/database/data/bahamas/bahamas_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/bahamas/bahamas_precious_metals.xlsx
@@ -587,17 +587,20 @@
           <t>Precious Metals</t>
         </is>
       </c>
+      <c r="E2">
+        <v>-0.201</v>
+      </c>
       <c r="K2">
-        <v>1.15</v>
+        <v>0.057</v>
       </c>
       <c r="M2">
-        <v>0.418</v>
+        <v>0.11</v>
       </c>
       <c r="N2">
-        <v>0.01117647058823529</v>
+        <v>0.003716216216216216</v>
       </c>
       <c r="O2">
-        <v>0.3634782608695653</v>
+        <v>1.929824561403509</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -609,37 +612,37 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.418</v>
+        <v>0.11</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>6.55</v>
+        <v>6.35</v>
       </c>
       <c r="V2">
-        <v>0.1751336898395722</v>
+        <v>0.214527027027027</v>
       </c>
       <c r="W2">
-        <v>0.1195426195426195</v>
+        <v>0.005377358490566038</v>
       </c>
       <c r="X2">
-        <v>0.08981085139738704</v>
+        <v>0.1898126434485412</v>
       </c>
       <c r="Y2">
-        <v>0.02973176814523251</v>
+        <v>-0.1844352849579752</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0.1936951863388341</v>
+        <v>0.1975308641975309</v>
       </c>
       <c r="AB2">
-        <v>0.08981085139738704</v>
+        <v>0.1898126434485412</v>
       </c>
       <c r="AC2">
-        <v>0.1038843349414471</v>
+        <v>0.007718220748989674</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -651,7 +654,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-6.55</v>
+        <v>-6.35</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -660,25 +663,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.2123176661264182</v>
+        <v>-0.2731182795698924</v>
       </c>
       <c r="AK2">
-        <v>-1.658227848101266</v>
+        <v>-1.494117647058824</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.046</v>
+        <v>-0.056</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-4.198717948717949</v>
+        <v>-3.649425287356322</v>
       </c>
       <c r="AQ2">
-        <v>-29.78260869565218</v>
+        <v>-28.57142857142857</v>
       </c>
     </row>
     <row r="3">
@@ -697,17 +700,20 @@
           <t>Precious Metals</t>
         </is>
       </c>
+      <c r="E3">
+        <v>-0.201</v>
+      </c>
       <c r="K3">
-        <v>1.15</v>
+        <v>0.057</v>
       </c>
       <c r="M3">
-        <v>0.418</v>
+        <v>0.11</v>
       </c>
       <c r="N3">
-        <v>0.01117647058823529</v>
+        <v>0.003716216216216216</v>
       </c>
       <c r="O3">
-        <v>0.3634782608695653</v>
+        <v>1.929824561403509</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -719,37 +725,37 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0.418</v>
+        <v>0.11</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>6.55</v>
+        <v>6.35</v>
       </c>
       <c r="V3">
-        <v>0.1751336898395722</v>
+        <v>0.214527027027027</v>
       </c>
       <c r="W3">
-        <v>0.1195426195426195</v>
+        <v>0.005377358490566038</v>
       </c>
       <c r="X3">
-        <v>0.08981085139738704</v>
+        <v>0.1898126434485412</v>
       </c>
       <c r="Y3">
-        <v>0.02973176814523251</v>
+        <v>-0.1844352849579752</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.1936951863388341</v>
+        <v>0.1975308641975309</v>
       </c>
       <c r="AB3">
-        <v>0.08981085139738704</v>
+        <v>0.1898126434485412</v>
       </c>
       <c r="AC3">
-        <v>0.1038843349414471</v>
+        <v>0.007718220748989674</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -761,7 +767,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-6.55</v>
+        <v>-6.35</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -770,25 +776,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.2123176661264182</v>
+        <v>-0.2731182795698924</v>
       </c>
       <c r="AK3">
-        <v>-1.658227848101266</v>
+        <v>-1.494117647058824</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.046</v>
+        <v>-0.056</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-4.198717948717949</v>
+        <v>-3.649425287356322</v>
       </c>
       <c r="AQ3">
-        <v>-29.78260869565218</v>
+        <v>-28.57142857142857</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bahamas/bahamas_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/bahamas/bahamas_precious_metals.xlsx
@@ -588,19 +588,19 @@
         </is>
       </c>
       <c r="E2">
-        <v>-0.201</v>
+        <v>0.0232</v>
       </c>
       <c r="K2">
-        <v>0.057</v>
+        <v>1.61</v>
       </c>
       <c r="M2">
-        <v>0.11</v>
+        <v>0.133</v>
       </c>
       <c r="N2">
-        <v>0.003716216216216216</v>
+        <v>0.003575268817204301</v>
       </c>
       <c r="O2">
-        <v>1.929824561403509</v>
+        <v>0.08260869565217391</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -612,37 +612,37 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.11</v>
+        <v>0.133</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>6.35</v>
+        <v>8.44</v>
       </c>
       <c r="V2">
-        <v>0.214527027027027</v>
+        <v>0.2268817204301075</v>
       </c>
       <c r="W2">
-        <v>0.005377358490566038</v>
+        <v>0.1518867924528302</v>
       </c>
       <c r="X2">
-        <v>0.1898126434485412</v>
+        <v>0.1545732499402778</v>
       </c>
       <c r="Y2">
-        <v>-0.1844352849579752</v>
+        <v>-0.002686457487447558</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0.1975308641975309</v>
+        <v>0.3746663706992231</v>
       </c>
       <c r="AB2">
-        <v>0.1898126434485412</v>
+        <v>0.1545732499402778</v>
       </c>
       <c r="AC2">
-        <v>0.007718220748989674</v>
+        <v>0.2200931207589453</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -654,7 +654,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-6.35</v>
+        <v>-8.44</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -663,25 +663,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.2731182795698924</v>
+        <v>-0.2934631432545201</v>
       </c>
       <c r="AK2">
-        <v>-1.494117647058824</v>
+        <v>-2.131313131313131</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.056</v>
+        <v>-0.143</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-3.649425287356322</v>
+        <v>-3.296875</v>
       </c>
       <c r="AQ2">
-        <v>-28.57142857142857</v>
+        <v>-16.5034965034965</v>
       </c>
     </row>
     <row r="3">
@@ -701,19 +701,19 @@
         </is>
       </c>
       <c r="E3">
-        <v>-0.201</v>
+        <v>0.0232</v>
       </c>
       <c r="K3">
-        <v>0.057</v>
+        <v>1.61</v>
       </c>
       <c r="M3">
-        <v>0.11</v>
+        <v>0.133</v>
       </c>
       <c r="N3">
-        <v>0.003716216216216216</v>
+        <v>0.003575268817204301</v>
       </c>
       <c r="O3">
-        <v>1.929824561403509</v>
+        <v>0.08260869565217391</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -725,37 +725,37 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0.11</v>
+        <v>0.133</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>6.35</v>
+        <v>8.44</v>
       </c>
       <c r="V3">
-        <v>0.214527027027027</v>
+        <v>0.2268817204301075</v>
       </c>
       <c r="W3">
-        <v>0.005377358490566038</v>
+        <v>0.1518867924528302</v>
       </c>
       <c r="X3">
-        <v>0.1898126434485412</v>
+        <v>0.1545732499402778</v>
       </c>
       <c r="Y3">
-        <v>-0.1844352849579752</v>
+        <v>-0.002686457487447558</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.1975308641975309</v>
+        <v>0.3746663706992231</v>
       </c>
       <c r="AB3">
-        <v>0.1898126434485412</v>
+        <v>0.1545732499402778</v>
       </c>
       <c r="AC3">
-        <v>0.007718220748989674</v>
+        <v>0.2200931207589453</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -767,7 +767,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-6.35</v>
+        <v>-8.44</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -776,25 +776,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.2731182795698924</v>
+        <v>-0.2934631432545201</v>
       </c>
       <c r="AK3">
-        <v>-1.494117647058824</v>
+        <v>-2.131313131313131</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.056</v>
+        <v>-0.143</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-3.649425287356322</v>
+        <v>-3.296875</v>
       </c>
       <c r="AQ3">
-        <v>-28.57142857142857</v>
+        <v>-16.5034965034965</v>
       </c>
     </row>
   </sheetData>
